--- a/Analisis_Financiero/7003748 - ANALISIS FINANCIERO-PRIMER PARICAL MECATRONICA A.xlsx
+++ b/Analisis_Financiero/7003748 - ANALISIS FINANCIERO-PRIMER PARICAL MECATRONICA A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres Felipe\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Semestre\Cursando\Analisis_Financiero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDD4455-5A42-4726-9BC2-ED35405A95F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BE3F71-C963-4748-93A5-9046041E1290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="887" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -410,10 +410,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="#,##0.000"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="28" x14ac:knownFonts="1">
     <font>
@@ -1134,7 +1136,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="219">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1458,6 +1460,68 @@
     <xf numFmtId="0" fontId="22" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1524,67 +1588,17 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6220,7 +6234,7 @@
   <cols>
     <col min="1" max="1" width="35" style="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33" style="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" style="28" customWidth="1"/>
     <col min="4" max="4" width="8.28515625" style="25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="28" customWidth="1"/>
     <col min="6" max="6" width="22.42578125" style="25" bestFit="1" customWidth="1"/>
@@ -6229,95 +6243,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="185" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="201"/>
-      <c r="C1" s="201"/>
-      <c r="D1" s="201"/>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
       <c r="E1" s="12"/>
-      <c r="H1" s="177" t="s">
+      <c r="H1" s="199" t="s">
         <v>95</v>
       </c>
-      <c r="I1" s="178"/>
-      <c r="J1" s="178"/>
-      <c r="K1" s="178"/>
-      <c r="L1" s="178"/>
-      <c r="M1" s="178"/>
-      <c r="N1" s="179"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="200"/>
+      <c r="K1" s="200"/>
+      <c r="L1" s="200"/>
+      <c r="M1" s="200"/>
+      <c r="N1" s="201"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="202"/>
-      <c r="B2" s="203"/>
-      <c r="C2" s="203"/>
-      <c r="D2" s="203"/>
+      <c r="A2" s="187"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
       <c r="E2" s="12"/>
-      <c r="H2" s="180"/>
-      <c r="I2" s="181"/>
-      <c r="J2" s="181"/>
-      <c r="K2" s="181"/>
-      <c r="L2" s="181"/>
-      <c r="M2" s="181"/>
-      <c r="N2" s="182"/>
+      <c r="H2" s="202"/>
+      <c r="I2" s="203"/>
+      <c r="J2" s="203"/>
+      <c r="K2" s="203"/>
+      <c r="L2" s="203"/>
+      <c r="M2" s="203"/>
+      <c r="N2" s="204"/>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="204" t="s">
+      <c r="A3" s="189" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="205"/>
-      <c r="C3" s="197">
+      <c r="B3" s="190"/>
+      <c r="C3" s="173">
         <v>2023</v>
       </c>
-      <c r="D3" s="198"/>
+      <c r="D3" s="174"/>
       <c r="E3" s="12"/>
-      <c r="F3" s="197">
+      <c r="F3" s="173">
         <v>2022</v>
       </c>
-      <c r="G3" s="198"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
-      <c r="L3" s="172"/>
-      <c r="M3" s="172"/>
-      <c r="N3" s="173"/>
+      <c r="G3" s="174"/>
+      <c r="H3" s="205"/>
+      <c r="I3" s="194"/>
+      <c r="J3" s="194"/>
+      <c r="K3" s="194"/>
+      <c r="L3" s="194"/>
+      <c r="M3" s="194"/>
+      <c r="N3" s="195"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="206" t="s">
+      <c r="A4" s="171" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="193"/>
+      <c r="C4" s="33">
+        <f>+'HOSPIRA VERTICAL B. G. '!B13</f>
+        <v>11782182718</v>
+      </c>
+      <c r="D4" s="180">
+        <f>+C4/C5</f>
+        <v>1.8699992219562109</v>
+      </c>
       <c r="E4" s="27"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="193"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="185"/>
-      <c r="K4" s="185"/>
-      <c r="L4" s="185"/>
-      <c r="M4" s="185"/>
-      <c r="N4" s="186"/>
+      <c r="F4" s="33">
+        <f>+'HOSPIRA VERTICAL B. G. '!C13</f>
+        <v>12246408943</v>
+      </c>
+      <c r="G4" s="180">
+        <f>+F4/F5</f>
+        <v>1.8068723714584536</v>
+      </c>
+      <c r="H4" s="206"/>
+      <c r="I4" s="207"/>
+      <c r="J4" s="207"/>
+      <c r="K4" s="207"/>
+      <c r="L4" s="207"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="208"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="207"/>
+      <c r="A5" s="172"/>
       <c r="B5" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="194"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="194"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="175"/>
-      <c r="L5" s="175"/>
-      <c r="M5" s="175"/>
-      <c r="N5" s="176"/>
+      <c r="C5" s="34">
+        <f>+'HOSPIRA VERTICAL B. G. '!E13</f>
+        <v>6300635091</v>
+      </c>
+      <c r="D5" s="181"/>
+      <c r="F5" s="34">
+        <f>+'HOSPIRA VERTICAL B. G. '!F13</f>
+        <v>6777683436</v>
+      </c>
+      <c r="G5" s="181"/>
+      <c r="H5" s="196"/>
+      <c r="I5" s="197"/>
+      <c r="J5" s="197"/>
+      <c r="K5" s="197"/>
+      <c r="L5" s="197"/>
+      <c r="M5" s="197"/>
+      <c r="N5" s="198"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="37"/>
@@ -6325,42 +6357,60 @@
       <c r="F6" s="29"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="206" t="s">
+      <c r="A7" s="171" t="s">
         <v>78</v>
       </c>
       <c r="B7" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="193"/>
+      <c r="C7" s="33">
+        <f>+'HOSPIRA VERTICAL B. G. '!B13-'HOSPIRA VERTICAL B. G. '!B9</f>
+        <v>9645946486</v>
+      </c>
+      <c r="D7" s="180">
+        <f>+C7/C8</f>
+        <v>1.5309482848448936</v>
+      </c>
       <c r="E7" s="30"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="193"/>
-      <c r="H7" s="187"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="188"/>
-      <c r="K7" s="188"/>
-      <c r="L7" s="188"/>
-      <c r="M7" s="188"/>
-      <c r="N7" s="189"/>
+      <c r="F7" s="33">
+        <f>+'HOSPIRA VERTICAL B. G. '!C13-'HOSPIRA VERTICAL B. G. '!C9</f>
+        <v>8220168133</v>
+      </c>
+      <c r="G7" s="180">
+        <f>+F7/F8</f>
+        <v>1.2128285734530138</v>
+      </c>
+      <c r="H7" s="209"/>
+      <c r="I7" s="210"/>
+      <c r="J7" s="210"/>
+      <c r="K7" s="210"/>
+      <c r="L7" s="210"/>
+      <c r="M7" s="210"/>
+      <c r="N7" s="211"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="207"/>
+      <c r="A8" s="172"/>
       <c r="B8" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="194"/>
+      <c r="C8" s="34">
+        <f>+'HOSPIRA VERTICAL B. G. '!E13</f>
+        <v>6300635091</v>
+      </c>
+      <c r="D8" s="181"/>
       <c r="E8" s="30"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="194"/>
-      <c r="H8" s="190"/>
-      <c r="I8" s="191"/>
-      <c r="J8" s="191"/>
-      <c r="K8" s="191"/>
-      <c r="L8" s="191"/>
-      <c r="M8" s="191"/>
-      <c r="N8" s="192"/>
+      <c r="F8" s="34">
+        <f>+'HOSPIRA VERTICAL B. G. '!F13</f>
+        <v>6777683436</v>
+      </c>
+      <c r="G8" s="181"/>
+      <c r="H8" s="212"/>
+      <c r="I8" s="213"/>
+      <c r="J8" s="213"/>
+      <c r="K8" s="213"/>
+      <c r="L8" s="213"/>
+      <c r="M8" s="213"/>
+      <c r="N8" s="214"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="37"/>
@@ -6371,17 +6421,17 @@
       <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="206" t="s">
+      <c r="A10" s="171" t="s">
         <v>81</v>
       </c>
       <c r="B10" s="40" t="s">
         <v>56</v>
       </c>
       <c r="C10" s="41"/>
-      <c r="D10" s="199"/>
+      <c r="D10" s="182"/>
       <c r="E10" s="14"/>
       <c r="F10" s="41"/>
-      <c r="G10" s="199"/>
+      <c r="G10" s="182"/>
       <c r="H10" s="39"/>
       <c r="I10" s="69"/>
       <c r="J10" s="69"/>
@@ -6391,13 +6441,19 @@
       <c r="N10" s="70"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="207"/>
+      <c r="A11" s="172"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="199"/>
+      <c r="C11" s="34">
+        <f>+C4-C5</f>
+        <v>5481547627</v>
+      </c>
+      <c r="D11" s="182"/>
       <c r="E11" s="14"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="199"/>
+      <c r="F11" s="34">
+        <f>+F4-F5</f>
+        <v>5468725507</v>
+      </c>
+      <c r="G11" s="182"/>
       <c r="H11" s="71"/>
       <c r="I11" s="72"/>
       <c r="J11" s="72"/>
@@ -6407,53 +6463,71 @@
       <c r="N11" s="73"/>
     </row>
     <row r="12" spans="1:14" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="213" t="s">
+      <c r="A12" s="177" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="213"/>
-      <c r="C12" s="213"/>
-      <c r="D12" s="214"/>
+      <c r="B12" s="177"/>
+      <c r="C12" s="177"/>
+      <c r="D12" s="178"/>
       <c r="E12" s="14"/>
       <c r="F12" s="15"/>
       <c r="G12" s="31"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="206" t="s">
+      <c r="A13" s="171" t="s">
         <v>58</v>
       </c>
       <c r="B13" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="193"/>
+      <c r="C13" s="33">
+        <f>+'HOSPIRA VERTICAL B. G. '!E20</f>
+        <v>16100635091</v>
+      </c>
+      <c r="D13" s="180">
+        <f>+C13/C14</f>
+        <v>0.43416867618767868</v>
+      </c>
       <c r="E13" s="14"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="193"/>
-      <c r="H13" s="171"/>
-      <c r="I13" s="172"/>
-      <c r="J13" s="172"/>
-      <c r="K13" s="172"/>
-      <c r="L13" s="172"/>
-      <c r="M13" s="172"/>
-      <c r="N13" s="173"/>
+      <c r="F13" s="33">
+        <f>+'HOSPIRA VERTICAL B. G. '!F20</f>
+        <v>17777683436</v>
+      </c>
+      <c r="G13" s="180">
+        <f>+F13/F14</f>
+        <v>0.61899728470790927</v>
+      </c>
+      <c r="H13" s="193"/>
+      <c r="I13" s="194"/>
+      <c r="J13" s="194"/>
+      <c r="K13" s="194"/>
+      <c r="L13" s="194"/>
+      <c r="M13" s="194"/>
+      <c r="N13" s="195"/>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="207"/>
+      <c r="A14" s="172"/>
       <c r="B14" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="194"/>
+      <c r="C14" s="34">
+        <f>+'HOSPIRA HORIZONTAL B. G.  '!B20</f>
+        <v>37083824730</v>
+      </c>
+      <c r="D14" s="181"/>
       <c r="E14" s="14"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="194"/>
-      <c r="H14" s="174"/>
-      <c r="I14" s="175"/>
-      <c r="J14" s="175"/>
-      <c r="K14" s="175"/>
-      <c r="L14" s="175"/>
-      <c r="M14" s="175"/>
-      <c r="N14" s="176"/>
+      <c r="F14" s="34">
+        <f>+'HOSPIRA HORIZONTAL B. G.  '!C20</f>
+        <v>28720131534</v>
+      </c>
+      <c r="G14" s="181"/>
+      <c r="H14" s="196"/>
+      <c r="I14" s="197"/>
+      <c r="J14" s="197"/>
+      <c r="K14" s="197"/>
+      <c r="L14" s="197"/>
+      <c r="M14" s="197"/>
+      <c r="N14" s="198"/>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="37"/>
@@ -6463,28 +6537,60 @@
       <c r="G15" s="31"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="206" t="s">
+      <c r="A16" s="171" t="s">
         <v>61</v>
       </c>
       <c r="B16" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="209"/>
+      <c r="C16" s="33">
+        <f>+'HOSPIRA VERTICAL B. G. '!E16+'HOSPIRA VERTICAL B. G. '!E7</f>
+        <v>9800000000</v>
+      </c>
+      <c r="D16" s="183">
+        <f>+C16/C17</f>
+        <v>0.33163614256561907</v>
+      </c>
       <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="31"/>
+      <c r="F16" s="33">
+        <f>+'HOSPIRA VERTICAL B. G. '!F16+'HOSPIRA VERTICAL B. G. '!F7</f>
+        <v>11000000000</v>
+      </c>
+      <c r="G16" s="180">
+        <f>+F16/F17</f>
+        <v>0.41911794093894467</v>
+      </c>
+      <c r="H16" s="193"/>
+      <c r="I16" s="194"/>
+      <c r="J16" s="194"/>
+      <c r="K16" s="194"/>
+      <c r="L16" s="194"/>
+      <c r="M16" s="194"/>
+      <c r="N16" s="195"/>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="207"/>
+      <c r="A17" s="172"/>
       <c r="B17" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="210"/>
+      <c r="C17" s="34">
+        <f>+'HOSPIRA VERTICAL E.R.'!D5</f>
+        <v>29550458295</v>
+      </c>
+      <c r="D17" s="184"/>
       <c r="E17" s="14"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="31"/>
+      <c r="F17" s="34">
+        <f>+'HOSPIRA VERTICAL E.R.'!C5</f>
+        <v>26245595632</v>
+      </c>
+      <c r="G17" s="181"/>
+      <c r="H17" s="196"/>
+      <c r="I17" s="197"/>
+      <c r="J17" s="197"/>
+      <c r="K17" s="197"/>
+      <c r="L17" s="197"/>
+      <c r="M17" s="197"/>
+      <c r="N17" s="198"/>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="37"/>
@@ -6494,42 +6600,60 @@
       <c r="G18" s="31"/>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="206" t="s">
+      <c r="A19" s="171" t="s">
         <v>64</v>
       </c>
       <c r="B19" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="193"/>
+      <c r="C19" s="33">
+        <f>+'HOSPIRA VERTICAL B. G. '!E13</f>
+        <v>6300635091</v>
+      </c>
+      <c r="D19" s="180">
+        <f>+C19/C20</f>
+        <v>0.39132835788086118</v>
+      </c>
       <c r="E19" s="14"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="193"/>
-      <c r="H19" s="171"/>
-      <c r="I19" s="172"/>
-      <c r="J19" s="172"/>
-      <c r="K19" s="172"/>
-      <c r="L19" s="172"/>
-      <c r="M19" s="172"/>
-      <c r="N19" s="173"/>
+      <c r="F19" s="33">
+        <f>+'HOSPIRA VERTICAL B. G. '!F13</f>
+        <v>6777683436</v>
+      </c>
+      <c r="G19" s="180">
+        <f>+F19/F20</f>
+        <v>0.38124671644648134</v>
+      </c>
+      <c r="H19" s="193"/>
+      <c r="I19" s="194"/>
+      <c r="J19" s="194"/>
+      <c r="K19" s="194"/>
+      <c r="L19" s="194"/>
+      <c r="M19" s="194"/>
+      <c r="N19" s="195"/>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="207"/>
+      <c r="A20" s="172"/>
       <c r="B20" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="194"/>
+      <c r="C20" s="34">
+        <f>+'HOSPIRA VERTICAL B. G. '!E20</f>
+        <v>16100635091</v>
+      </c>
+      <c r="D20" s="181"/>
       <c r="E20" s="14"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="194"/>
-      <c r="H20" s="174"/>
-      <c r="I20" s="175"/>
-      <c r="J20" s="175"/>
-      <c r="K20" s="175"/>
-      <c r="L20" s="175"/>
-      <c r="M20" s="175"/>
-      <c r="N20" s="176"/>
+      <c r="F20" s="34">
+        <f>+'HOSPIRA VERTICAL B. G. '!F20</f>
+        <v>17777683436</v>
+      </c>
+      <c r="G20" s="181"/>
+      <c r="H20" s="196"/>
+      <c r="I20" s="197"/>
+      <c r="J20" s="197"/>
+      <c r="K20" s="197"/>
+      <c r="L20" s="197"/>
+      <c r="M20" s="197"/>
+      <c r="N20" s="198"/>
     </row>
     <row r="21" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="37"/>
@@ -6539,65 +6663,95 @@
       <c r="G21" s="31"/>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="206" t="s">
+      <c r="A22" s="171" t="s">
         <v>67</v>
       </c>
       <c r="B22" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="195"/>
+      <c r="C22" s="33">
+        <f>+C20</f>
+        <v>16100635091</v>
+      </c>
+      <c r="D22" s="191">
+        <f>+C22/C23</f>
+        <v>0.76731113658120242</v>
+      </c>
       <c r="E22" s="14"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="195"/>
-      <c r="H22" s="171"/>
-      <c r="I22" s="172"/>
-      <c r="J22" s="172"/>
-      <c r="K22" s="172"/>
-      <c r="L22" s="172"/>
-      <c r="M22" s="172"/>
-      <c r="N22" s="173"/>
+      <c r="F22" s="33">
+        <f>+F20</f>
+        <v>17777683436</v>
+      </c>
+      <c r="G22" s="191">
+        <f>+F22/F23</f>
+        <v>1.6246532107608813</v>
+      </c>
+      <c r="H22" s="193"/>
+      <c r="I22" s="194"/>
+      <c r="J22" s="194"/>
+      <c r="K22" s="194"/>
+      <c r="L22" s="194"/>
+      <c r="M22" s="194"/>
+      <c r="N22" s="195"/>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="207"/>
+      <c r="A23" s="172"/>
       <c r="B23" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="196"/>
+      <c r="C23" s="34">
+        <f>+'HOSPIRA VERTICAL B. G. '!E29</f>
+        <v>20983189639</v>
+      </c>
+      <c r="D23" s="192"/>
       <c r="E23" s="14"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="196"/>
-      <c r="H23" s="174"/>
-      <c r="I23" s="175"/>
-      <c r="J23" s="175"/>
-      <c r="K23" s="175"/>
-      <c r="L23" s="175"/>
-      <c r="M23" s="175"/>
-      <c r="N23" s="176"/>
+      <c r="F23" s="34">
+        <f>+'HOSPIRA VERTICAL B. G. '!F29</f>
+        <v>10942448098</v>
+      </c>
+      <c r="G23" s="192"/>
+      <c r="H23" s="196"/>
+      <c r="I23" s="197"/>
+      <c r="J23" s="197"/>
+      <c r="K23" s="197"/>
+      <c r="L23" s="197"/>
+      <c r="M23" s="197"/>
+      <c r="N23" s="198"/>
     </row>
     <row r="24" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="212" t="s">
+      <c r="A24" s="176" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="212"/>
-      <c r="C24" s="212"/>
-      <c r="D24" s="212"/>
+      <c r="B24" s="176"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="176"/>
       <c r="E24" s="14"/>
       <c r="F24" s="16"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="206" t="s">
+      <c r="A25" s="171" t="s">
         <v>89</v>
       </c>
       <c r="B25" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="193"/>
+      <c r="C25" s="35">
+        <f>+'HOSPIRA VERTICAL E.R.'!D5</f>
+        <v>29550458295</v>
+      </c>
+      <c r="D25" s="215">
+        <f>+C25/C26</f>
+        <v>8.7335924735270649E-3</v>
+      </c>
       <c r="E25" s="14"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="193"/>
+      <c r="F25" s="33">
+        <f>+'HOSPIRA VERTICAL E.R.'!C5</f>
+        <v>26245595632</v>
+      </c>
+      <c r="G25" s="215">
+        <f>+F25/F26</f>
+        <v>1.0428343389970195E-2</v>
+      </c>
       <c r="H25" s="74"/>
       <c r="I25" s="75"/>
       <c r="J25" s="75"/>
@@ -6607,15 +6761,21 @@
       <c r="N25" s="76"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="207"/>
+      <c r="A26" s="172"/>
       <c r="B26" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="36"/>
-      <c r="D26" s="194"/>
+      <c r="C26" s="36">
+        <f>+'HOSPIRA VERTICAL B. G. '!B8 * 360</f>
+        <v>3383539864560</v>
+      </c>
+      <c r="D26" s="216"/>
       <c r="E26" s="14"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="194"/>
+      <c r="F26" s="34">
+        <f>+'HOSPIRA VERTICAL B. G. '!C8 * 360</f>
+        <v>2516755984200</v>
+      </c>
+      <c r="G26" s="216"/>
       <c r="H26" s="77"/>
       <c r="I26" s="78"/>
       <c r="J26" s="78"/>
@@ -6633,90 +6793,126 @@
       <c r="F27" s="16"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="206" t="s">
+      <c r="A28" s="171" t="s">
         <v>88</v>
       </c>
       <c r="B28" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="C28" s="35"/>
-      <c r="D28" s="193"/>
+      <c r="C28" s="35">
+        <f>+'HOSPIRA VERTICAL B. G. '!B9</f>
+        <v>2136236232</v>
+      </c>
+      <c r="D28" s="217">
+        <f>+C28/C29</f>
+        <v>4.0776612821634661E-4</v>
+      </c>
       <c r="E28" s="14"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="193"/>
-      <c r="H28" s="171"/>
-      <c r="I28" s="172"/>
-      <c r="J28" s="172"/>
-      <c r="K28" s="172"/>
-      <c r="L28" s="172"/>
-      <c r="M28" s="172"/>
-      <c r="N28" s="173"/>
+      <c r="F28" s="35">
+        <f>+'HOSPIRA VERTICAL B. G. '!C9</f>
+        <v>4026240810</v>
+      </c>
+      <c r="G28" s="217">
+        <f>+F28/F29</f>
+        <v>8.2688511258760403E-4</v>
+      </c>
+      <c r="H28" s="193"/>
+      <c r="I28" s="194"/>
+      <c r="J28" s="194"/>
+      <c r="K28" s="194"/>
+      <c r="L28" s="194"/>
+      <c r="M28" s="194"/>
+      <c r="N28" s="195"/>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="207"/>
+      <c r="A29" s="172"/>
       <c r="B29" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="36"/>
-      <c r="D29" s="194"/>
+      <c r="C29" s="36">
+        <f>+'HOSPIRA VERTICAL E.R.'!D6*360</f>
+        <v>5238876120840</v>
+      </c>
+      <c r="D29" s="218"/>
       <c r="E29" s="14"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="194"/>
-      <c r="H29" s="174"/>
-      <c r="I29" s="175"/>
-      <c r="J29" s="175"/>
-      <c r="K29" s="175"/>
-      <c r="L29" s="175"/>
-      <c r="M29" s="175"/>
-      <c r="N29" s="176"/>
+      <c r="F29" s="36">
+        <f>+'HOSPIRA VERTICAL E.R.'!C6*360</f>
+        <v>4869165920040</v>
+      </c>
+      <c r="G29" s="218"/>
+      <c r="H29" s="196"/>
+      <c r="I29" s="197"/>
+      <c r="J29" s="197"/>
+      <c r="K29" s="197"/>
+      <c r="L29" s="197"/>
+      <c r="M29" s="197"/>
+      <c r="N29" s="198"/>
     </row>
     <row r="30" spans="1:14" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="211" t="s">
+      <c r="A30" s="175" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="212"/>
-      <c r="C30" s="212"/>
-      <c r="D30" s="212"/>
+      <c r="B30" s="176"/>
+      <c r="C30" s="176"/>
+      <c r="D30" s="176"/>
       <c r="E30" s="14"/>
       <c r="F30" s="16"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="206" t="s">
+      <c r="A31" s="171" t="s">
         <v>71</v>
       </c>
       <c r="B31" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="35"/>
-      <c r="D31" s="193"/>
+      <c r="C31" s="35">
+        <f>+'HOSPIRA VERTICAL E.R.'!D7</f>
+        <v>14998024626</v>
+      </c>
+      <c r="D31" s="180">
+        <f>+C31/C32</f>
+        <v>0.50753949317048996</v>
+      </c>
       <c r="E31" s="14"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="193"/>
-      <c r="H31" s="171"/>
-      <c r="I31" s="172"/>
-      <c r="J31" s="172"/>
-      <c r="K31" s="172"/>
-      <c r="L31" s="172"/>
-      <c r="M31" s="172"/>
-      <c r="N31" s="173"/>
+      <c r="F31" s="33">
+        <f>+'HOSPIRA VERTICAL E.R.'!C7</f>
+        <v>12720134743</v>
+      </c>
+      <c r="G31" s="180">
+        <f>+F31/F32</f>
+        <v>0.48465788017746292</v>
+      </c>
+      <c r="H31" s="193"/>
+      <c r="I31" s="194"/>
+      <c r="J31" s="194"/>
+      <c r="K31" s="194"/>
+      <c r="L31" s="194"/>
+      <c r="M31" s="194"/>
+      <c r="N31" s="195"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="207"/>
+      <c r="A32" s="172"/>
       <c r="B32" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="36"/>
-      <c r="D32" s="194"/>
+      <c r="C32" s="36">
+        <f>+'HOSPIRA VERTICAL E.R.'!D5</f>
+        <v>29550458295</v>
+      </c>
+      <c r="D32" s="181"/>
       <c r="E32" s="14"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="194"/>
-      <c r="H32" s="174"/>
-      <c r="I32" s="175"/>
-      <c r="J32" s="175"/>
-      <c r="K32" s="175"/>
-      <c r="L32" s="175"/>
-      <c r="M32" s="175"/>
-      <c r="N32" s="176"/>
+      <c r="F32" s="34">
+        <f>+'HOSPIRA VERTICAL E.R.'!C5</f>
+        <v>26245595632</v>
+      </c>
+      <c r="G32" s="181"/>
+      <c r="H32" s="196"/>
+      <c r="I32" s="197"/>
+      <c r="J32" s="197"/>
+      <c r="K32" s="197"/>
+      <c r="L32" s="197"/>
+      <c r="M32" s="197"/>
+      <c r="N32" s="198"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="37"/>
@@ -6725,42 +6921,60 @@
       <c r="F33" s="16"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="206" t="s">
+      <c r="A34" s="171" t="s">
         <v>74</v>
       </c>
       <c r="B34" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="35"/>
-      <c r="D34" s="193"/>
+      <c r="C34" s="35">
+        <f>+'HOSPIRA VERTICAL E.R.'!D9</f>
+        <v>2946316550</v>
+      </c>
+      <c r="D34" s="180">
+        <f>+C34/C35</f>
+        <v>9.9704597491759472E-2</v>
+      </c>
       <c r="E34" s="14"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="193"/>
-      <c r="H34" s="171"/>
-      <c r="I34" s="172"/>
-      <c r="J34" s="172"/>
-      <c r="K34" s="172"/>
-      <c r="L34" s="172"/>
-      <c r="M34" s="172"/>
-      <c r="N34" s="173"/>
+      <c r="F34" s="33">
+        <f>+'HOSPIRA VERTICAL E.R.'!C9</f>
+        <v>2061001673</v>
+      </c>
+      <c r="G34" s="180">
+        <f>+F34/F35</f>
+        <v>7.8527525223589106E-2</v>
+      </c>
+      <c r="H34" s="193"/>
+      <c r="I34" s="194"/>
+      <c r="J34" s="194"/>
+      <c r="K34" s="194"/>
+      <c r="L34" s="194"/>
+      <c r="M34" s="194"/>
+      <c r="N34" s="195"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="207"/>
+      <c r="A35" s="172"/>
       <c r="B35" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="36"/>
-      <c r="D35" s="194"/>
+      <c r="C35" s="36">
+        <f>+C32</f>
+        <v>29550458295</v>
+      </c>
+      <c r="D35" s="181"/>
       <c r="E35" s="14"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="194"/>
-      <c r="H35" s="174"/>
-      <c r="I35" s="175"/>
-      <c r="J35" s="175"/>
-      <c r="K35" s="175"/>
-      <c r="L35" s="175"/>
-      <c r="M35" s="175"/>
-      <c r="N35" s="176"/>
+      <c r="F35" s="34">
+        <f>+F32</f>
+        <v>26245595632</v>
+      </c>
+      <c r="G35" s="181"/>
+      <c r="H35" s="196"/>
+      <c r="I35" s="197"/>
+      <c r="J35" s="197"/>
+      <c r="K35" s="197"/>
+      <c r="L35" s="197"/>
+      <c r="M35" s="197"/>
+      <c r="N35" s="198"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="37"/>
@@ -6769,42 +6983,60 @@
       <c r="F36" s="16"/>
     </row>
     <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="206" t="s">
+      <c r="A37" s="171" t="s">
         <v>76</v>
       </c>
       <c r="B37" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="C37" s="35"/>
-      <c r="D37" s="193"/>
+      <c r="C37" s="35">
+        <f>+'HOSPIRA VERTICAL E.R.'!D16</f>
+        <v>1567319167</v>
+      </c>
+      <c r="D37" s="180">
+        <f>+C37/C38</f>
+        <v>5.3038743133983601E-2</v>
+      </c>
       <c r="E37" s="14"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="193"/>
-      <c r="H37" s="171"/>
-      <c r="I37" s="172"/>
-      <c r="J37" s="172"/>
-      <c r="K37" s="172"/>
-      <c r="L37" s="172"/>
-      <c r="M37" s="172"/>
-      <c r="N37" s="173"/>
+      <c r="F37" s="33">
+        <f>+'HOSPIRA VERTICAL E.R.'!C16</f>
+        <v>1065291928</v>
+      </c>
+      <c r="G37" s="180">
+        <f>+F37/F38</f>
+        <v>4.0589359942021681E-2</v>
+      </c>
+      <c r="H37" s="193"/>
+      <c r="I37" s="194"/>
+      <c r="J37" s="194"/>
+      <c r="K37" s="194"/>
+      <c r="L37" s="194"/>
+      <c r="M37" s="194"/>
+      <c r="N37" s="195"/>
     </row>
     <row r="38" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="207"/>
+      <c r="A38" s="172"/>
       <c r="B38" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="36"/>
-      <c r="D38" s="194"/>
+      <c r="C38" s="36">
+        <f>+C35</f>
+        <v>29550458295</v>
+      </c>
+      <c r="D38" s="181"/>
       <c r="E38" s="14"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="194"/>
-      <c r="H38" s="174"/>
-      <c r="I38" s="175"/>
-      <c r="J38" s="175"/>
-      <c r="K38" s="175"/>
-      <c r="L38" s="175"/>
-      <c r="M38" s="175"/>
-      <c r="N38" s="176"/>
+      <c r="F38" s="34">
+        <f>+F35</f>
+        <v>26245595632</v>
+      </c>
+      <c r="G38" s="181"/>
+      <c r="H38" s="196"/>
+      <c r="I38" s="197"/>
+      <c r="J38" s="197"/>
+      <c r="K38" s="197"/>
+      <c r="L38" s="197"/>
+      <c r="M38" s="197"/>
+      <c r="N38" s="198"/>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="37"/>
@@ -6813,42 +7045,60 @@
       <c r="F39" s="16"/>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="206" t="s">
+      <c r="A40" s="171" t="s">
         <v>83</v>
       </c>
       <c r="B40" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="193"/>
+      <c r="C40" s="35">
+        <f>+'HOSPIRA HORIZONTAL E. R.'!D17</f>
+        <v>1567319167</v>
+      </c>
+      <c r="D40" s="180">
+        <f>+C40/C41</f>
+        <v>7.4694038130739313E-2</v>
+      </c>
       <c r="E40" s="14"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="193"/>
-      <c r="H40" s="171"/>
-      <c r="I40" s="172"/>
-      <c r="J40" s="172"/>
-      <c r="K40" s="172"/>
-      <c r="L40" s="172"/>
-      <c r="M40" s="172"/>
-      <c r="N40" s="173"/>
+      <c r="F40" s="33">
+        <f>+'HOSPIRA HORIZONTAL E. R.'!C17</f>
+        <v>1065291928</v>
+      </c>
+      <c r="G40" s="180">
+        <f>+F40/F41</f>
+        <v>9.7354076387596314E-2</v>
+      </c>
+      <c r="H40" s="193"/>
+      <c r="I40" s="194"/>
+      <c r="J40" s="194"/>
+      <c r="K40" s="194"/>
+      <c r="L40" s="194"/>
+      <c r="M40" s="194"/>
+      <c r="N40" s="195"/>
     </row>
     <row r="41" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="207"/>
+      <c r="A41" s="172"/>
       <c r="B41" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="36"/>
-      <c r="D41" s="194"/>
+      <c r="C41" s="36">
+        <f>+'HOSPIRA VERTICAL B. G. '!E29</f>
+        <v>20983189639</v>
+      </c>
+      <c r="D41" s="181"/>
       <c r="E41" s="14"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="194"/>
-      <c r="H41" s="174"/>
-      <c r="I41" s="175"/>
-      <c r="J41" s="175"/>
-      <c r="K41" s="175"/>
-      <c r="L41" s="175"/>
-      <c r="M41" s="175"/>
-      <c r="N41" s="176"/>
+      <c r="F41" s="34">
+        <f>+'HOSPIRA VERTICAL B. G. '!F29</f>
+        <v>10942448098</v>
+      </c>
+      <c r="G41" s="181"/>
+      <c r="H41" s="196"/>
+      <c r="I41" s="197"/>
+      <c r="J41" s="197"/>
+      <c r="K41" s="197"/>
+      <c r="L41" s="197"/>
+      <c r="M41" s="197"/>
+      <c r="N41" s="198"/>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="37"/>
@@ -6858,42 +7108,60 @@
       <c r="F42" s="16"/>
     </row>
     <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="206" t="s">
+      <c r="A43" s="171" t="s">
         <v>84</v>
       </c>
       <c r="B43" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="193"/>
+      <c r="C43" s="35">
+        <f>+C40</f>
+        <v>1567319167</v>
+      </c>
+      <c r="D43" s="180">
+        <f>+C43/C44</f>
+        <v>4.2264226476404231E-2</v>
+      </c>
       <c r="E43" s="14"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="193"/>
-      <c r="H43" s="171"/>
-      <c r="I43" s="172"/>
-      <c r="J43" s="172"/>
-      <c r="K43" s="172"/>
-      <c r="L43" s="172"/>
-      <c r="M43" s="172"/>
-      <c r="N43" s="173"/>
+      <c r="F43" s="35">
+        <f>+F40</f>
+        <v>1065291928</v>
+      </c>
+      <c r="G43" s="180">
+        <f>+F43/F44</f>
+        <v>3.7092167448427818E-2</v>
+      </c>
+      <c r="H43" s="193"/>
+      <c r="I43" s="194"/>
+      <c r="J43" s="194"/>
+      <c r="K43" s="194"/>
+      <c r="L43" s="194"/>
+      <c r="M43" s="194"/>
+      <c r="N43" s="195"/>
     </row>
     <row r="44" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="207"/>
+      <c r="A44" s="172"/>
       <c r="B44" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="36"/>
-      <c r="D44" s="194"/>
+      <c r="C44" s="36">
+        <f>+'HOSPIRA VERTICAL B. G. '!B20</f>
+        <v>37083824730</v>
+      </c>
+      <c r="D44" s="181"/>
       <c r="E44" s="14"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="194"/>
-      <c r="H44" s="174"/>
-      <c r="I44" s="175"/>
-      <c r="J44" s="175"/>
-      <c r="K44" s="175"/>
-      <c r="L44" s="175"/>
-      <c r="M44" s="175"/>
-      <c r="N44" s="176"/>
+      <c r="F44" s="36">
+        <f>+'HOSPIRA VERTICAL B. G. '!C20</f>
+        <v>28720131534</v>
+      </c>
+      <c r="G44" s="181"/>
+      <c r="H44" s="196"/>
+      <c r="I44" s="197"/>
+      <c r="J44" s="197"/>
+      <c r="K44" s="197"/>
+      <c r="L44" s="197"/>
+      <c r="M44" s="197"/>
+      <c r="N44" s="198"/>
     </row>
     <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
@@ -6907,7 +7175,7 @@
       <c r="A46" s="12"/>
       <c r="B46" s="14"/>
       <c r="C46" s="13"/>
-      <c r="D46" s="208"/>
+      <c r="D46" s="179"/>
       <c r="E46" s="14"/>
       <c r="F46" s="84"/>
     </row>
@@ -6915,7 +7183,7 @@
       <c r="A47" s="12"/>
       <c r="B47" s="14"/>
       <c r="C47" s="13"/>
-      <c r="D47" s="208"/>
+      <c r="D47" s="179"/>
       <c r="E47" s="14"/>
       <c r="F47" s="16"/>
     </row>
@@ -6923,7 +7191,7 @@
       <c r="A48" s="12"/>
       <c r="B48" s="14"/>
       <c r="C48" s="13"/>
-      <c r="D48" s="208"/>
+      <c r="D48" s="179"/>
       <c r="E48" s="17"/>
       <c r="F48" s="16"/>
     </row>
@@ -6931,7 +7199,7 @@
       <c r="A49" s="12"/>
       <c r="B49" s="14"/>
       <c r="C49" s="13"/>
-      <c r="D49" s="208"/>
+      <c r="D49" s="179"/>
       <c r="E49" s="17"/>
       <c r="F49" s="16"/>
     </row>
@@ -7371,29 +7639,35 @@
       <c r="C129" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="D40:D41"/>
+  <mergeCells count="64">
+    <mergeCell ref="H43:N44"/>
+    <mergeCell ref="H1:N2"/>
+    <mergeCell ref="H28:N29"/>
+    <mergeCell ref="H31:N32"/>
+    <mergeCell ref="H34:N35"/>
+    <mergeCell ref="H37:N38"/>
+    <mergeCell ref="H40:N41"/>
+    <mergeCell ref="H3:N5"/>
+    <mergeCell ref="H7:N8"/>
+    <mergeCell ref="H13:N14"/>
+    <mergeCell ref="H19:N20"/>
+    <mergeCell ref="H22:N23"/>
+    <mergeCell ref="H16:N17"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G31:G32"/>
     <mergeCell ref="A1:D2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A34:A35"/>
@@ -7408,32 +7682,28 @@
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A31:A32"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H43:N44"/>
-    <mergeCell ref="H1:N2"/>
-    <mergeCell ref="H28:N29"/>
-    <mergeCell ref="H31:N32"/>
-    <mergeCell ref="H34:N35"/>
-    <mergeCell ref="H37:N38"/>
-    <mergeCell ref="H40:N41"/>
-    <mergeCell ref="H3:N5"/>
-    <mergeCell ref="H7:N8"/>
-    <mergeCell ref="H13:N14"/>
-    <mergeCell ref="H19:N20"/>
-    <mergeCell ref="H22:N23"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
